--- a/htr-ML-Sections/ig/StructureDefinition-fr-lm-supporting-information.xlsx
+++ b/htr-ML-Sections/ig/StructureDefinition-fr-lm-supporting-information.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T12:47:35+00:00</t>
+    <t>2026-05-07T13:30:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-ML-Sections/ig/StructureDefinition-fr-lm-supporting-information.xlsx
+++ b/htr-ML-Sections/ig/StructureDefinition-fr-lm-supporting-information.xlsx
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Modèle logique métier - FR LM Supporting Information</t>
+    <t>Logical model - FR LM Supporting Information</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T13:30:39+00:00</t>
+    <t>2026-05-12T13:21:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -385,19 +385,19 @@
     <t>Résultats d'examens antérieurs pertinents</t>
   </si>
   <si>
-    <t>fr-lm-supporting-information.entry.antecedentsMedicaux</t>
+    <t>fr-lm-supporting-information.entry.historyOfPastIllness</t>
   </si>
   <si>
     <t>Observation</t>
   </si>
   <si>
-    <t>fr-lm-supporting-information.entry.antecedentsChirurgicaux</t>
-  </si>
-  <si>
-    <t>fr-lm-supporting-information.entry.contreIndications</t>
-  </si>
-  <si>
-    <t>fr-lm-supporting-information.entry.probleme</t>
+    <t>fr-lm-supporting-information.entry.historyOfPastProcedures</t>
+  </si>
+  <si>
+    <t>fr-lm-supporting-information.entry.contraIndication</t>
+  </si>
+  <si>
+    <t>fr-lm-supporting-information.entry.condition</t>
   </si>
   <si>
     <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-condition
@@ -407,7 +407,7 @@
     <t>Problème</t>
   </si>
   <si>
-    <t>fr-lm-supporting-information.entry.dispositifMedical</t>
+    <t>fr-lm-supporting-information.entry.device</t>
   </si>
   <si>
     <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-device-use
@@ -417,7 +417,7 @@
     <t>Dispositif médical</t>
   </si>
   <si>
-    <t>fr-lm-supporting-information.entry.statutGrossesse</t>
+    <t>fr-lm-supporting-information.entry.pregnancyStatus</t>
   </si>
   <si>
     <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-pregnancy-observation
@@ -427,7 +427,7 @@
     <t>Statut grossesse</t>
   </si>
   <si>
-    <t>fr-lm-supporting-information.entry.administrationProduitDeSante</t>
+    <t>fr-lm-supporting-information.entry.priorMedicationAdministration</t>
   </si>
   <si>
     <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-dicom-medication-administration
@@ -437,7 +437,7 @@
     <t>Produits de santé administré avant l'examen d'imagerie</t>
   </si>
   <si>
-    <t>fr-lm-supporting-information.entry.sexeClinique</t>
+    <t>fr-lm-supporting-information.entry.sexForClinicalUse</t>
   </si>
   <si>
     <t>Sexe Clinique</t>
@@ -745,8 +745,8 @@
   <dimension ref="A1:AJ21"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="52.21875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="52.21875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="52.296875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="52.296875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -776,7 +776,7 @@
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="52.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="52.296875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -2808,7 +2808,7 @@
         <v>74</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>73</v>
@@ -2883,7 +2883,7 @@
         <v>74</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>73</v>
